--- a/xls/square_un_16_tri3_13.xlsx
+++ b/xls/square_un_16_tri3_13.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>238</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>340</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>174</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>906</v>
+      </c>
+      <c r="I11">
+        <v>-0.00022052834610198458</v>
+      </c>
+      <c r="J11">
+        <v>-1.5702372525749735</v>
+      </c>
+      <c r="K11">
+        <v>-0.053478192826221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>238</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>340</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>209</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>1104</v>
+      </c>
+      <c r="I12">
+        <v>-0.00021444799455624887</v>
+      </c>
+      <c r="J12">
+        <v>-1.3694096045087942</v>
+      </c>
+      <c r="K12">
+        <v>0.5731619642908283</v>
+      </c>
+    </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F13">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13">
-        <v>1014</v>
+        <v>1266</v>
       </c>
       <c r="I13">
-        <v>-1.610842746905647</v>
+        <v>-0.00019658996883942104</v>
       </c>
       <c r="J13">
-        <v>-1.7853458989028632</v>
+        <v>-1.0236226209948065</v>
       </c>
       <c r="K13">
-        <v>-0.6951027225512537</v>
+        <v>1.3766117554437785</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F14">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
       <c r="H14">
-        <v>1176</v>
+        <v>1362</v>
       </c>
       <c r="I14">
-        <v>-2.0134029323626974</v>
+        <v>-0.0001740603276496375</v>
       </c>
       <c r="J14">
-        <v>-2.0021518172202692</v>
+        <v>-0.7695043490899672</v>
       </c>
       <c r="K14">
-        <v>-0.8239861947630874</v>
+        <v>1.6918024041981619</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F15">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15">
-        <v>1350</v>
+        <v>1596</v>
       </c>
       <c r="I15">
-        <v>-2.4562611865371373</v>
+        <v>-0.00016261294835957213</v>
       </c>
       <c r="J15">
-        <v>-2.033157916596396</v>
+        <v>-0.661207963955895</v>
       </c>
       <c r="K15">
-        <v>-0.6245802717681526</v>
+        <v>2.28513963573657</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1536</v>
+        <v>1842</v>
       </c>
       <c r="I16">
-        <v>-2.136016701822907</v>
+        <v>-0.00010274942239168802</v>
       </c>
       <c r="J16">
-        <v>-1.7497563303391876</v>
+        <v>-0.3493083199702773</v>
       </c>
       <c r="K16">
-        <v>-0.0887093418553122</v>
+        <v>2.905346931322772</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B17">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17">
-        <v>1734</v>
+        <v>2070</v>
       </c>
       <c r="I17">
-        <v>-1.6754483476119209</v>
+        <v>-2.8070931424545958e-5</v>
       </c>
       <c r="J17">
-        <v>-1.4366766289722832</v>
+        <v>-0.08529287635584396</v>
       </c>
       <c r="K17">
-        <v>0.42532376850713466</v>
+        <v>3.2289521545609388</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B18">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>1944</v>
+        <v>2388</v>
       </c>
       <c r="I18">
-        <v>-1.1912346010415007</v>
+        <v>-5.027704784223988e-8</v>
       </c>
       <c r="J18">
-        <v>-1.0463306034668347</v>
+        <v>-0.00011724792544181294</v>
       </c>
       <c r="K18">
-        <v>1.0450733705654849</v>
+        <v>2.469221326786757</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B19">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-0.4832578617561783</v>
+        <v>-4.598400225591971e-9</v>
       </c>
       <c r="J19">
-        <v>-0.4319338444832524</v>
+        <v>-9.430055709509554e-6</v>
       </c>
       <c r="K19">
-        <v>1.7530600962515794</v>
+        <v>1.9298491909894537</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>-0.01483785237546744</v>
+        <v>-1.2017870315917975e-9</v>
       </c>
       <c r="J20">
-        <v>-0.015066189416471627</v>
+        <v>-2.196502754844652e-6</v>
       </c>
       <c r="K20">
-        <v>2.9940518424431564</v>
+        <v>1.6104946347884745</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-8.310864715841861e-5</v>
+        <v>-1.0954119720422224e-9</v>
       </c>
       <c r="J21">
-        <v>-0.00010711646146726567</v>
+        <v>-2.114771134578767e-6</v>
       </c>
       <c r="K21">
-        <v>2.5436668336900112</v>
+        <v>1.606633558725789</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-1.8232258535914808e-5</v>
+        <v>-7.366283924713878e-10</v>
       </c>
       <c r="J22">
-        <v>-2.0492341044841673e-5</v>
+        <v>-1.497946138533292e-6</v>
       </c>
       <c r="K22">
-        <v>2.157123725429886</v>
+        <v>1.5380929418287246</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-8.039407757947535e-6</v>
+        <v>-5.358211317993825e-10</v>
       </c>
       <c r="J23">
-        <v>-1.0108099298904235e-5</v>
+        <v>-1.1030955240410446e-6</v>
       </c>
       <c r="K23">
-        <v>2.011844223738958</v>
+        <v>1.475114144554452</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-7.930316213553008e-6</v>
+        <v>-5.130591462513721e-10</v>
       </c>
       <c r="J24">
-        <v>-9.269241392504837e-6</v>
+        <v>-1.049647763053722e-6</v>
       </c>
       <c r="K24">
-        <v>1.9826867912899484</v>
+        <v>1.4615707389804007</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -881,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-3.250181505705676e-6</v>
+        <v>-4.414823739151546e-10</v>
       </c>
       <c r="J25">
-        <v>-4.1248513361962946e-6</v>
+        <v>-9.211990564796725e-7</v>
       </c>
       <c r="K25">
-        <v>1.8159337085002623</v>
+        <v>1.4367845995653097</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -916,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-3.0003681797981795e-6</v>
+        <v>-3.9648444346370026e-10</v>
       </c>
       <c r="J26">
-        <v>-3.943067426857257e-6</v>
+        <v>-8.224762114415115e-7</v>
       </c>
       <c r="K26">
-        <v>1.8097430125815037</v>
+        <v>1.4115289838520997</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -951,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -963,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-2.0178452419304006e-6</v>
+        <v>-3.6759314432397545e-10</v>
       </c>
       <c r="J27">
-        <v>-2.7625226169464167e-6</v>
+        <v>-7.636830582158019e-7</v>
       </c>
       <c r="K27">
-        <v>1.7436443543491826</v>
+        <v>1.3958049211631767</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -986,7 +1056,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -998,22 +1068,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-1.8849173148112548e-6</v>
+        <v>-3.582041628035272e-10</v>
       </c>
       <c r="J28">
-        <v>-2.5962793513171645e-6</v>
+        <v>-7.438489803861647e-7</v>
       </c>
       <c r="K28">
-        <v>1.7252181230495824</v>
+        <v>1.390628880984718</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1021,7 +1091,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -1033,22 +1103,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-1.188222661651656e-6</v>
+        <v>-3.775010786712031e-10</v>
       </c>
       <c r="J29">
-        <v>-1.793010187174468e-6</v>
+        <v>-7.840883094298278e-7</v>
       </c>
       <c r="K29">
-        <v>1.6544863832957815</v>
+        <v>1.4018867102986274</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1056,7 +1126,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -1068,22 +1138,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-1.4319557812678738e-6</v>
+        <v>-3.295692301235266e-10</v>
       </c>
       <c r="J30">
-        <v>-1.7744349044094393e-6</v>
+        <v>-6.857124806571819e-7</v>
       </c>
       <c r="K30">
-        <v>1.6206052669768884</v>
+        <v>1.3728118402706577</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1091,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -1103,22 +1173,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-1.3867581387868256e-6</v>
+        <v>-3.2538525432486367e-10</v>
       </c>
       <c r="J31">
-        <v>-1.5214148365957178e-6</v>
+        <v>-6.756949711075945e-7</v>
       </c>
       <c r="K31">
-        <v>1.5644974313075168</v>
+        <v>1.369556304888898</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1126,7 +1196,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1138,22 +1208,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-1.4400972968760363e-6</v>
+        <v>-3.1473536642552054e-10</v>
       </c>
       <c r="J32">
-        <v>-1.473167968542345e-6</v>
+        <v>-6.568279707968243e-7</v>
       </c>
       <c r="K32">
-        <v>1.5409728978366077</v>
+        <v>1.3638429214238292</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_13.xlsx
+++ b/xls/square_un_16_tri3_13.xlsx
@@ -482,13 +482,13 @@
         <v>906</v>
       </c>
       <c r="I11">
-        <v>-0.00022052834610198458</v>
+        <v>-0.9595856198037355</v>
       </c>
       <c r="J11">
-        <v>-1.5702372525749735</v>
+        <v>-1.4959411558206024</v>
       </c>
       <c r="K11">
-        <v>-0.053478192826221</v>
+        <v>-0.5514482832878181</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1104</v>
       </c>
       <c r="I12">
-        <v>-0.00021444799455624887</v>
+        <v>-1.7151155407910237</v>
       </c>
       <c r="J12">
-        <v>-1.3694096045087942</v>
+        <v>-1.9510936659444995</v>
       </c>
       <c r="K12">
-        <v>0.5731619642908283</v>
+        <v>-0.9388037426587894</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1266</v>
       </c>
       <c r="I13">
-        <v>-0.00019658996883942104</v>
+        <v>-2.2012409503549795</v>
       </c>
       <c r="J13">
-        <v>-1.0236226209948065</v>
+        <v>-1.949129759183193</v>
       </c>
       <c r="K13">
-        <v>1.3766117554437785</v>
+        <v>-0.8736618848128411</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1362</v>
       </c>
       <c r="I14">
-        <v>-0.0001740603276496375</v>
+        <v>-2.271240947187978</v>
       </c>
       <c r="J14">
-        <v>-0.7695043490899672</v>
+        <v>-1.8541772325172596</v>
       </c>
       <c r="K14">
-        <v>1.6918024041981619</v>
+        <v>-0.5363860387261139</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1596</v>
       </c>
       <c r="I15">
-        <v>-0.00016261294835957213</v>
+        <v>-2.008215614910872</v>
       </c>
       <c r="J15">
-        <v>-0.661207963955895</v>
+        <v>-1.6261713020866346</v>
       </c>
       <c r="K15">
-        <v>2.28513963573657</v>
+        <v>-0.06331596998222917</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-0.00010274942239168802</v>
+        <v>-1.9006824943799208</v>
       </c>
       <c r="J16">
-        <v>-0.3493083199702773</v>
+        <v>-1.640185474481588</v>
       </c>
       <c r="K16">
-        <v>2.905346931322772</v>
+        <v>-0.24588569817790684</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2070</v>
       </c>
       <c r="I17">
-        <v>-2.8070931424545958e-5</v>
+        <v>-0.6337615189922583</v>
       </c>
       <c r="J17">
-        <v>-0.08529287635584396</v>
+        <v>-0.5656392310287573</v>
       </c>
       <c r="K17">
-        <v>3.2289521545609388</v>
+        <v>1.4140287897451649</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-5.027704784223988e-8</v>
+        <v>-0.1155702372152467</v>
       </c>
       <c r="J18">
-        <v>-0.00011724792544181294</v>
+        <v>-0.10578351767378434</v>
       </c>
       <c r="K18">
-        <v>2.469221326786757</v>
+        <v>2.4088021247954914</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-4.598400225591971e-9</v>
+        <v>-1.1602235344120067e-5</v>
       </c>
       <c r="J19">
-        <v>-9.430055709509554e-6</v>
+        <v>-1.4912486785486642e-5</v>
       </c>
       <c r="K19">
-        <v>1.9298491909894537</v>
+        <v>2.0828408753729857</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -797,13 +797,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-1.2017870315917975e-9</v>
+        <v>1.096092730544844e-6</v>
       </c>
       <c r="J20">
-        <v>-2.196502754844652e-6</v>
+        <v>-1.130533649039689e-6</v>
       </c>
       <c r="K20">
-        <v>1.6104946347884745</v>
+        <v>1.7427658541805786</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -832,13 +832,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.0954119720422224e-9</v>
+        <v>-8.809281787491391e-7</v>
       </c>
       <c r="J21">
-        <v>-2.114771134578767e-6</v>
+        <v>-1.7934947583270239e-6</v>
       </c>
       <c r="K21">
-        <v>1.606633558725789</v>
+        <v>1.6855689508838676</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -867,13 +867,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-7.366283924713878e-10</v>
+        <v>-8.528609978441108e-7</v>
       </c>
       <c r="J22">
-        <v>-1.497946138533292e-6</v>
+        <v>-1.2918648957394743e-6</v>
       </c>
       <c r="K22">
-        <v>1.5380929418287246</v>
+        <v>1.5790437373567512</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -902,13 +902,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-5.358211317993825e-10</v>
+        <v>-7.443157562296789e-7</v>
       </c>
       <c r="J23">
-        <v>-1.1030955240410446e-6</v>
+        <v>-9.97958824331182e-7</v>
       </c>
       <c r="K23">
-        <v>1.475114144554452</v>
+        <v>1.5071328927541203</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -937,13 +937,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-5.130591462513721e-10</v>
+        <v>-6.606401848979718e-7</v>
       </c>
       <c r="J24">
-        <v>-1.049647763053722e-6</v>
+        <v>-9.234375466742107e-7</v>
       </c>
       <c r="K24">
-        <v>1.4615707389804007</v>
+        <v>1.495308540049451</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -972,13 +972,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-4.414823739151546e-10</v>
+        <v>-7.762928679445378e-7</v>
       </c>
       <c r="J25">
-        <v>-9.211990564796725e-7</v>
+        <v>-8.926036127694461e-7</v>
       </c>
       <c r="K25">
-        <v>1.4367845995653097</v>
+        <v>1.4534154753804753</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-3.9648444346370026e-10</v>
+        <v>-6.136325457463591e-7</v>
       </c>
       <c r="J26">
-        <v>-8.224762114415115e-7</v>
+        <v>-7.552354575936935e-7</v>
       </c>
       <c r="K26">
-        <v>1.4115289838520997</v>
+        <v>1.429757276973782</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-3.6759314432397545e-10</v>
+        <v>-6.581620971084558e-7</v>
       </c>
       <c r="J27">
-        <v>-7.636830582158019e-7</v>
+        <v>-7.445726707204026e-7</v>
       </c>
       <c r="K27">
-        <v>1.3958049211631767</v>
+        <v>1.410493335008667</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-3.582041628035272e-10</v>
+        <v>-6.534733241946267e-7</v>
       </c>
       <c r="J28">
-        <v>-7.438489803861647e-7</v>
+        <v>-7.283073659943624e-7</v>
       </c>
       <c r="K28">
-        <v>1.390628880984718</v>
+        <v>1.4032077933776892</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-3.775010786712031e-10</v>
+        <v>-7.134279896563008e-7</v>
       </c>
       <c r="J29">
-        <v>-7.840883094298278e-7</v>
+        <v>-7.784845708879716e-7</v>
       </c>
       <c r="K29">
-        <v>1.4018867102986274</v>
+        <v>1.4133177034332167</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-3.295692301235266e-10</v>
+        <v>-6.019847327810982e-7</v>
       </c>
       <c r="J30">
-        <v>-6.857124806571819e-7</v>
+        <v>-6.714879740512824e-7</v>
       </c>
       <c r="K30">
-        <v>1.3728118402706577</v>
+        <v>1.3850609045805804</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1182,13 +1182,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-3.2538525432486367e-10</v>
+        <v>-6.308980161584305e-7</v>
       </c>
       <c r="J31">
-        <v>-6.756949711075945e-7</v>
+        <v>-6.808177723888631e-7</v>
       </c>
       <c r="K31">
-        <v>1.369556304888898</v>
+        <v>1.380980123703558</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-3.1473536642552054e-10</v>
+        <v>-5.900516505571814e-7</v>
       </c>
       <c r="J32">
-        <v>-6.568279707968243e-7</v>
+        <v>-6.513353377508498e-7</v>
       </c>
       <c r="K32">
-        <v>1.3638429214238292</v>
+        <v>1.3762711580305111</v>
       </c>
     </row>
   </sheetData>
